--- a/Apostas_Diarias/Apostas_20260423.xlsx
+++ b/Apostas_Diarias/Apostas_20260423.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_2B590F4F9546CE68CA55FB91591510344D07F757" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F47E035-62C6-4B6F-8762-587F1844D8B0}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_2B590F4F9526405DD103C4F0504C68377491FA2F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D26F50AA-B216-4FAB-92E7-A95B2CE18E11}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
   <si>
     <t>Data</t>
   </si>
@@ -74,22 +74,37 @@
     <t>P1 ⭐</t>
   </si>
   <si>
-    <t>13:00:00</t>
-  </si>
-  <si>
-    <t>SERBIA 1</t>
-  </si>
-  <si>
-    <t>FK Napredak x FK IMT Novi Beograd</t>
+    <t>13:10:00</t>
+  </si>
+  <si>
+    <t>SAUDI ARABIA 1</t>
+  </si>
+  <si>
+    <t>Al Najma Club x Al-Taawoun Buraidah</t>
   </si>
   <si>
     <t>Lay_CS_0x1_B365</t>
   </si>
   <si>
-    <t>15:00:00</t>
-  </si>
-  <si>
-    <t>FK Spartak x FK Backa Topola</t>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>SPAIN 1</t>
+  </si>
+  <si>
+    <t>Levante x Sevilla</t>
+  </si>
+  <si>
+    <t>16:30:00</t>
+  </si>
+  <si>
+    <t>Oviedo x Villarreal</t>
+  </si>
+  <si>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>Lay_CS_1x0_B365</t>
   </si>
 </sst>
 </file>
@@ -429,13 +444,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="37" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="39" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -478,9 +494,6 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1">
-        <v>500</v>
-      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -502,26 +515,24 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>9.8000000000000007</v>
+        <v>11</v>
       </c>
       <c r="H2">
-        <f>G2</f>
-        <v>9.8000000000000007</v>
+        <v>11</v>
       </c>
       <c r="I2">
-        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
         <f>IF(L2=1,"GREEN","RED")</f>
-        <v>RED</v>
+        <v>GREEN</v>
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>-500</v>
+        <v>46.75</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -535,34 +546,112 @@
         <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
       </c>
       <c r="G3">
-        <v>9.8000000000000007</v>
+        <v>10.5</v>
       </c>
       <c r="H3">
-        <f>G3</f>
-        <v>9.8000000000000007</v>
+        <v>10.5</v>
       </c>
       <c r="I3">
-        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f>IF(L3=1,"GREEN","RED")</f>
+        <f t="shared" ref="J3:J5" si="0">IF(L3=1,"GREEN","RED")</f>
         <v>GREEN</v>
       </c>
       <c r="K3">
-        <f>IF(L3=1,0.935/(H3-1)*I3,-500)</f>
-        <v>53.125</v>
+        <f t="shared" ref="K3:K5" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>49.210526315789473</v>
       </c>
       <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4">
+        <v>9.6</v>
+      </c>
+      <c r="H4">
+        <v>9.6</v>
+      </c>
+      <c r="I4">
+        <v>500</v>
+      </c>
+      <c r="J4" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="1"/>
+        <v>54.360465116279073</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>9</v>
+      </c>
+      <c r="I5">
+        <v>500</v>
+      </c>
+      <c r="J5" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="1"/>
+        <v>58.4375</v>
+      </c>
+      <c r="L5">
         <v>1</v>
       </c>
     </row>
